--- a/public/data/employee_data.xlsx
+++ b/public/data/employee_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosappiahnkum/Herd/hrms/public/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosappiahnkum/Desktop/cashpoint/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8A8802-5344-3041-AD9C-E0E874CD79D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D844A9-5F74-D140-971B-D788A8820233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="266">
   <si>
     <t>Staff ID</t>
   </si>
@@ -99,12 +99,6 @@
     <t>IT</t>
   </si>
   <si>
-    <t>RECOVERY</t>
-  </si>
-  <si>
-    <t>SECURITY</t>
-  </si>
-  <si>
     <t xml:space="preserve">info@cashpointgh.com </t>
   </si>
   <si>
@@ -645,15 +639,9 @@
     <t>OPERATIONS MANAGER</t>
   </si>
   <si>
-    <t>EXECUTIVE ASSISTANT</t>
-  </si>
-  <si>
     <t>INTERNAL AUDIT MANAGER</t>
   </si>
   <si>
-    <t>CUSTOMER SERIVCE MANAGER</t>
-  </si>
-  <si>
     <t>CREDIT MANAGER</t>
   </si>
   <si>
@@ -687,13 +675,154 @@
     <t>CHIEF TELLER</t>
   </si>
   <si>
-    <t>CUSTOMER SERVICE OFFICER</t>
-  </si>
-  <si>
     <t>TELLER</t>
   </si>
   <si>
     <t>SALES EXECUTIVE</t>
+  </si>
+  <si>
+    <t>CMB00001</t>
+  </si>
+  <si>
+    <t>CMB00002</t>
+  </si>
+  <si>
+    <t>CMB00003</t>
+  </si>
+  <si>
+    <t>CMB00004</t>
+  </si>
+  <si>
+    <t>CMB00005</t>
+  </si>
+  <si>
+    <t>CMB00006</t>
+  </si>
+  <si>
+    <t>CMB00007</t>
+  </si>
+  <si>
+    <t>CMB00008</t>
+  </si>
+  <si>
+    <t>CMB00009</t>
+  </si>
+  <si>
+    <t>CMB00010</t>
+  </si>
+  <si>
+    <t>CMB00011</t>
+  </si>
+  <si>
+    <t>CMB00012</t>
+  </si>
+  <si>
+    <t>CMB00013</t>
+  </si>
+  <si>
+    <t>CMB00014</t>
+  </si>
+  <si>
+    <t>CMB00015</t>
+  </si>
+  <si>
+    <t>CMB00016</t>
+  </si>
+  <si>
+    <t>CMB00017</t>
+  </si>
+  <si>
+    <t>CMB00018</t>
+  </si>
+  <si>
+    <t>CMB00019</t>
+  </si>
+  <si>
+    <t>CMB00020</t>
+  </si>
+  <si>
+    <t>CMB00021</t>
+  </si>
+  <si>
+    <t>CMB00022</t>
+  </si>
+  <si>
+    <t>CMB00023</t>
+  </si>
+  <si>
+    <t>CMB00024</t>
+  </si>
+  <si>
+    <t>CMB00025</t>
+  </si>
+  <si>
+    <t>CMB00026</t>
+  </si>
+  <si>
+    <t>CMB00027</t>
+  </si>
+  <si>
+    <t>CMB00028</t>
+  </si>
+  <si>
+    <t>CMB00029</t>
+  </si>
+  <si>
+    <t>CMB00030</t>
+  </si>
+  <si>
+    <t>CMB00031</t>
+  </si>
+  <si>
+    <t>CMB00032</t>
+  </si>
+  <si>
+    <t>CMB00033</t>
+  </si>
+  <si>
+    <t>CMB00034</t>
+  </si>
+  <si>
+    <t>CMB00035</t>
+  </si>
+  <si>
+    <t>CMB00036</t>
+  </si>
+  <si>
+    <t>CMB00037</t>
+  </si>
+  <si>
+    <t>CMB00038</t>
+  </si>
+  <si>
+    <t>CMB00039</t>
+  </si>
+  <si>
+    <t>CMB00040</t>
+  </si>
+  <si>
+    <t>CMB00041</t>
+  </si>
+  <si>
+    <t>CMB00042</t>
+  </si>
+  <si>
+    <t>CMB00043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RISK &amp; COMPLIANCE </t>
+  </si>
+  <si>
+    <t>ABAWIERE</t>
+  </si>
+  <si>
+    <t>CUSTOMER SERVICE MANAGER</t>
+  </si>
+  <si>
+    <t>RISK &amp; COMPLIANCE MANAGER</t>
+  </si>
+  <si>
+    <t>EXECUTIVE ASSISTANT &amp; HR MANAGER</t>
   </si>
 </sst>
 </file>
@@ -704,7 +833,7 @@
     <numFmt numFmtId="164" formatCode="[$]yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -728,6 +857,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -1154,13 +1289,13 @@
   <dimension ref="A1:AME44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -1221,15 +1356,17 @@
       </c>
     </row>
     <row r="2" spans="1:1019" s="6" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="B2"/>
+      <c r="B2" t="s">
+        <v>218</v>
+      </c>
       <c r="C2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F2"/>
       <c r="G2" s="3"/>
@@ -1237,17 +1374,17 @@
         <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L2"/>
       <c r="M2" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
@@ -1258,15 +1395,17 @@
       <c r="AME2"/>
     </row>
     <row r="3" spans="1:1019" s="6" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="B3"/>
+      <c r="B3" t="s">
+        <v>219</v>
+      </c>
       <c r="C3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F3"/>
       <c r="G3" s="3"/>
@@ -1274,17 +1413,17 @@
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L3"/>
       <c r="M3" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
@@ -1295,31 +1434,35 @@
       <c r="AME3"/>
     </row>
     <row r="4" spans="1:1019" s="6" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="B4"/>
+      <c r="B4" t="s">
+        <v>220</v>
+      </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E4"/>
+        <v>107</v>
+      </c>
+      <c r="E4" t="s">
+        <v>262</v>
+      </c>
       <c r="F4"/>
       <c r="G4" s="3"/>
       <c r="H4" t="s">
         <v>19</v>
       </c>
       <c r="I4" t="s">
-        <v>206</v>
+        <v>265</v>
       </c>
       <c r="J4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L4"/>
       <c r="M4" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
@@ -1330,15 +1473,17 @@
       <c r="AME4"/>
     </row>
     <row r="5" spans="1:1019" s="6" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="B5"/>
+      <c r="B5" t="s">
+        <v>221</v>
+      </c>
       <c r="C5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F5"/>
       <c r="G5" s="3"/>
@@ -1346,17 +1491,17 @@
         <v>20</v>
       </c>
       <c r="I5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L5"/>
       <c r="M5" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
@@ -1367,15 +1512,17 @@
       <c r="AME5"/>
     </row>
     <row r="6" spans="1:1019" s="6" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="B6"/>
+      <c r="B6" t="s">
+        <v>222</v>
+      </c>
       <c r="C6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F6"/>
       <c r="G6" s="3"/>
@@ -1383,17 +1530,17 @@
         <v>21</v>
       </c>
       <c r="I6" t="s">
-        <v>208</v>
+        <v>263</v>
       </c>
       <c r="J6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L6"/>
       <c r="M6" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
@@ -1404,12 +1551,14 @@
       <c r="AME6"/>
     </row>
     <row r="7" spans="1:1019" s="6" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7"/>
+      <c r="B7" t="s">
+        <v>223</v>
+      </c>
       <c r="C7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E7"/>
       <c r="F7"/>
@@ -1418,17 +1567,17 @@
         <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L7"/>
       <c r="M7" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
@@ -1439,884 +1588,996 @@
       <c r="AME7"/>
     </row>
     <row r="8" spans="1:1019" ht="16" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>224</v>
+      </c>
       <c r="C8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" t="s">
         <v>113</v>
-      </c>
-      <c r="E8" t="s">
-        <v>115</v>
       </c>
       <c r="H8" t="s">
         <v>23</v>
       </c>
       <c r="I8" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P8" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:1019" ht="16" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>225</v>
+      </c>
       <c r="C9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
       </c>
       <c r="I9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:1019" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>226</v>
+      </c>
       <c r="C10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:1019" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>227</v>
+      </c>
       <c r="C11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H11" t="s">
-        <v>22</v>
+        <v>261</v>
       </c>
       <c r="I11" t="s">
-        <v>212</v>
+        <v>264</v>
       </c>
       <c r="J11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:1019" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>228</v>
+      </c>
       <c r="C12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H12" t="s">
         <v>22</v>
       </c>
       <c r="I12" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J12" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" t="s">
+        <v>33</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1019" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>229</v>
+      </c>
+      <c r="C13" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" t="s">
+        <v>151</v>
+      </c>
+      <c r="H13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" t="s">
+        <v>209</v>
+      </c>
+      <c r="J13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" t="s">
+        <v>97</v>
+      </c>
+      <c r="M13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1019" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" t="s">
+        <v>152</v>
+      </c>
+      <c r="H14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" t="s">
+        <v>210</v>
+      </c>
+      <c r="J14" t="s">
         <v>59</v>
       </c>
-      <c r="M12" t="s">
-        <v>35</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1019" ht="16" x14ac:dyDescent="0.2">
-      <c r="C13" t="s">
-        <v>190</v>
-      </c>
-      <c r="D13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="K14" t="s">
+        <v>98</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1019" ht="16" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C15" t="s">
         <v>153</v>
       </c>
-      <c r="H13" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" t="s">
-        <v>213</v>
-      </c>
-      <c r="J13" t="s">
-        <v>60</v>
-      </c>
-      <c r="K13" t="s">
-        <v>99</v>
-      </c>
-      <c r="M13" t="s">
-        <v>36</v>
-      </c>
-      <c r="P13" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1019" ht="16" x14ac:dyDescent="0.2">
-      <c r="C14" t="s">
-        <v>191</v>
-      </c>
-      <c r="D14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" t="s">
-        <v>154</v>
-      </c>
-      <c r="H14" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" t="s">
-        <v>214</v>
-      </c>
-      <c r="J14" t="s">
-        <v>61</v>
-      </c>
-      <c r="K14" t="s">
-        <v>100</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1019" ht="16" x14ac:dyDescent="0.2">
-      <c r="C15" t="s">
-        <v>155</v>
-      </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:1019" ht="16" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>232</v>
+      </c>
       <c r="C16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
       </c>
       <c r="I16" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>233</v>
+      </c>
       <c r="C17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H17" t="s">
         <v>21</v>
       </c>
       <c r="I17" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P17" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>234</v>
+      </c>
       <c r="C18" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H18" t="s">
         <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K18" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>235</v>
+      </c>
       <c r="C19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H19" t="s">
         <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P19" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>236</v>
+      </c>
       <c r="C20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H20" t="s">
         <v>22</v>
       </c>
       <c r="I20" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>237</v>
+      </c>
       <c r="C21" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H21" t="s">
         <v>21</v>
       </c>
       <c r="I21" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>238</v>
+      </c>
       <c r="C22" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H22" t="s">
         <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>239</v>
+      </c>
       <c r="C23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E23" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H23" t="s">
         <v>22</v>
       </c>
       <c r="I23" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="J23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M23" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P23" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>240</v>
+      </c>
       <c r="C24" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H24" t="s">
         <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>241</v>
+      </c>
       <c r="C25" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H25" t="s">
         <v>22</v>
       </c>
       <c r="I25" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P25" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>242</v>
+      </c>
       <c r="C26" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H26" t="s">
         <v>22</v>
       </c>
       <c r="I26" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>243</v>
+      </c>
       <c r="C27" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D27" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H27" t="s">
         <v>22</v>
       </c>
       <c r="I27" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K27" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>244</v>
+      </c>
       <c r="C28" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D28" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E28" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H28" t="s">
         <v>22</v>
       </c>
       <c r="I28" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J28" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>245</v>
+      </c>
       <c r="C29" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D29" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E29" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H29" t="s">
         <v>22</v>
       </c>
       <c r="I29" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>246</v>
+      </c>
       <c r="C30" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D30" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H30" t="s">
         <v>22</v>
       </c>
       <c r="I30" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>247</v>
+      </c>
       <c r="C31" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D31" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H31" t="s">
         <v>22</v>
       </c>
       <c r="I31" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J31" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K31" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="P31" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>248</v>
+      </c>
       <c r="C32" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D32" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H32" t="s">
         <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J32" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>249</v>
+      </c>
       <c r="C33" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H33" t="s">
         <v>22</v>
       </c>
       <c r="I33" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J33" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P33" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>250</v>
+      </c>
       <c r="C34" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D34" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J34" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M34" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>251</v>
+      </c>
       <c r="C35" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D35" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E35" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H35" t="s">
         <v>21</v>
       </c>
       <c r="I35" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="J35" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M35" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P35" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>252</v>
+      </c>
       <c r="C36" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D36" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="J36" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>253</v>
+      </c>
       <c r="C37" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D37" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E37" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H37" t="s">
         <v>21</v>
       </c>
       <c r="I37" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J37" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K37" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="P37" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>254</v>
+      </c>
       <c r="C38" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D38" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H38" t="s">
         <v>21</v>
       </c>
       <c r="I38" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J38" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>255</v>
+      </c>
       <c r="C39" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D39" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H39" t="s">
         <v>21</v>
       </c>
       <c r="I39" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="P39" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>256</v>
+      </c>
       <c r="C40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H40" t="s">
         <v>21</v>
       </c>
       <c r="I40" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>257</v>
+      </c>
       <c r="C41" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D41" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E41" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H41" t="s">
         <v>21</v>
       </c>
       <c r="I41" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J41" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>258</v>
+      </c>
       <c r="C42" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D42" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E42" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H42" t="s">
         <v>21</v>
       </c>
       <c r="I42" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>259</v>
+      </c>
       <c r="C43" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D43" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E43" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H43" t="s">
         <v>21</v>
       </c>
       <c r="I43" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J43" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="3:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>260</v>
+      </c>
       <c r="C44" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D44" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E44" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H44" t="s">
         <v>21</v>
       </c>
       <c r="I44" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J44" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
